--- a/Document/1st_Year_Faculty_Details.xlsx
+++ b/Document/1st_Year_Faculty_Details.xlsx
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -799,7 +799,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>1st Year Sec-B</t>
+          <t>1st Year Sec-B, 1st Year Sec-D</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -1064,12 +1064,12 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Mrs.A.VANI BERLIN</t>
+          <t>Mr.KUMARASAMY</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>ENG</t>
+          <t>EEE</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>EN25C01 - ENGLISH ESSENTIALS-I</t>
+          <t>ME25C16 - MAKERSPACE</t>
         </is>
       </c>
     </row>
@@ -1089,17 +1089,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Mr.KUMARASAMY</t>
+          <t>Mrs.VYSHNAVAI</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>EEE</t>
+          <t>CIVIL</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>1st Year Sec-D</t>
+          <t>1st Year Sec-D, 1st Year Sec-G</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -1114,22 +1114,22 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Mrs.VYSHNAVAI</t>
+          <t>Mr.ARAVIND</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>CIVIL</t>
+          <t>ENG</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>1st Year Sec-D, 1st Year Sec-G</t>
+          <t>1st Year Sec-E, 1st Year Sec-F</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>ME25C16 - MAKERSPACE</t>
+          <t>EN25C01 - ENGLISH ESSENTIALS-I</t>
         </is>
       </c>
     </row>
@@ -1139,22 +1139,22 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Mr.ARAVIND</t>
+          <t>Mr.VIJAYAKUMAR</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>ENG</t>
+          <t>MECH</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>1st Year Sec-E, 1st Year Sec-F</t>
+          <t>1st Year Sec-E</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>EN25C01 - ENGLISH ESSENTIALS-I</t>
+          <t>ME25C03 - INTRODUCTION TO MECHANICAL ENGINEERING</t>
         </is>
       </c>
     </row>
@@ -1164,7 +1164,7 @@
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Mr.VIJAYAKUMAR</t>
+          <t>Mr.KALAIMANII</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>ME25C03 - INTRODUCTION TO MECHANICAL ENGINEERING</t>
+          <t>ME25C16 - MAKERSPACE</t>
         </is>
       </c>
     </row>
@@ -1189,22 +1189,22 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Mr.KALAIMANII</t>
+          <t>Mrs.AMUDHA</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>MECH</t>
+          <t>ECE</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>1st Year Sec-E</t>
+          <t>1st Year Sec-F</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>ME25C16 - MAKERSPACE</t>
+          <t>EE25C03 - FUNDAMENTALS OF ELEC &amp; ELEC ENG, ME25C16 - MAKERSPACE</t>
         </is>
       </c>
     </row>
@@ -1214,12 +1214,12 @@
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>Mrs.AMUDHA</t>
+          <t>MS.GOPHIKA</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>ECE</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>EE25C03 - FUNDAMENTALS OF ELEC &amp; ELEC ENG, ME25C16 - MAKERSPACE</t>
+          <t>TT25C01 - INTRODUCTION TO TEXTILE TECH</t>
         </is>
       </c>
     </row>
@@ -1239,22 +1239,22 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>MS.GOPHIKA</t>
+          <t>Mr.KUMARASWAMY</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>EEE</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>1st Year Sec-F</t>
+          <t>1st Year Sec-F, 1st Year Sec-G</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>TT25C01 - INTRODUCTION TO TEXTILE TECH</t>
+          <t>EI25C01 - INTRODUCTION TO MEASUREMENT, EE25C04 - BASIC ELECTRONICS AND ELECTRICAL ENG</t>
         </is>
       </c>
     </row>
@@ -1264,22 +1264,22 @@
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>Mr.KUMARASWAMY</t>
+          <t>Mrs.R.SUMATHY</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>EEE</t>
+          <t>MATHS</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>1st Year Sec-F, 1st Year Sec-G</t>
+          <t>1st Year Sec-G</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>EI25C01 - INTRODUCTION TO MEASUREMENT, EE25C04 - BASIC ELECTRONICS AND ELECTRICAL ENG</t>
+          <t>MA25C01 - APPLIED CALCULUS</t>
         </is>
       </c>
     </row>
@@ -1289,22 +1289,22 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Mrs.R.SUMATHY</t>
+          <t>Mrs.G.REVATHY</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>MATHS</t>
+          <t>PHY</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>1st Year Sec-G</t>
+          <t>1st Year Sec-B, 1st Year Sec-G</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>MA25C01 - APPLIED CALCULUS</t>
+          <t>PH25C01 - APPLIED PHYSICS-I</t>
         </is>
       </c>
     </row>
@@ -1314,45 +1314,20 @@
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>Mrs.G.REVATHY</t>
+          <t>Mrs.ASHWINI</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>PHY</t>
+          <t>ECE</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>1st Year Sec-B, 1st Year Sec-G</t>
+          <t>1st Year Sec-G</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>PH25C01 - APPLIED PHYSICS-I</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="4" t="n">
-        <v>33</v>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>Mrs.ASHWINI</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>ECE</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="inlineStr">
-        <is>
-          <t>1st Year Sec-G</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="inlineStr">
         <is>
           <t>ME25C16 - MAKERSPACE</t>
         </is>
